--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_0_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_0_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>320071.425633411</v>
+        <v>320074.8015362156</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547405</v>
+        <v>2995243.613506387</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745723</v>
+        <v>20355670.24425594</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4812396.678818937</v>
+        <v>4812058.02286789</v>
       </c>
     </row>
     <row r="11">
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,16 +1165,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1183,13 +1183,13 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.91010078545518</v>
+        <v>10.61706312961832</v>
       </c>
     </row>
     <row r="9">
@@ -1211,16 +1211,16 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>22.15420867374215</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J9" t="n">
         <v>0.7465913262578567</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1320,19 +1320,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0.2968606583479769</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T10" t="n">
-        <v>19.82224313344376</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1369,19 +1369,19 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>26</v>
+        <v>10.61706312961832</v>
       </c>
       <c r="G11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I11" t="n">
-        <v>22.90079999999999</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1484,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>22.15420867374215</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1530,16 +1530,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.27419204266741</v>
+        <v>0.2968606583479769</v>
       </c>
       <c r="H13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K13" t="n">
         <v>22.26949182588285</v>
@@ -1606,16 +1606,16 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>10.95151064538747</v>
+        <v>10.61706312961832</v>
       </c>
       <c r="G14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -1685,19 +1685,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>22.90079999999999</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1767,16 +1767,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0.2968606583479769</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -1843,16 +1843,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="G17" t="n">
-        <v>2.722411430842662</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>28</v>
+        <v>12.35200489467393</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
         <v>11.94928935461252</v>
@@ -1876,10 +1876,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1913,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1928,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>28</v>
+        <v>24.30129424928645</v>
       </c>
     </row>
     <row r="19">
@@ -2040,16 +2040,16 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>22.02246762618612</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="T19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2071,10 +2071,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>230.1769504358686</v>
+        <v>94.41048699370604</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2116,19 +2116,19 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -2147,19 +2147,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>28.92645775760019</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -2195,28 +2195,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>162.4005985629044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2271,13 +2271,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="S22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2314,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>230.8476210749815</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2326,10 +2326,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2350,31 +2350,31 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>234.288905720311</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2384,28 +2384,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>49.23175083062949</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>11.13164595284859</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2432,13 +2432,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2447,13 +2447,13 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -2523,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2596,7 +2596,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2621,7 +2621,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>29.79900896488263</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>29.7578455661223</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
         <v>205.7729852034775</v>
@@ -2757,10 +2757,10 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -2779,16 +2779,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2839,16 +2839,16 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y29" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
         <v>172.7084989883157</v>
@@ -2870,16 +2870,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0.7465913262578567</v>
@@ -2906,13 +2906,13 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2921,13 +2921,13 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.02881784590195366</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>120.1278225855194</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>133.186967585368</v>
+        <v>110.9174757594852</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3025,19 +3025,19 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="H32" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3070,10 +3070,10 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>184.6464420572887</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>66.07950996323517</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
@@ -3107,19 +3107,19 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>104.9740769133399</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3143,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3158,13 +3158,13 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3234,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>110.9174757594852</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3298,10 +3298,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>29.51218284430547</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="Y35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="36">
@@ -3332,16 +3332,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>8.886618849664252</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -3353,10 +3353,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3383,10 +3383,10 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3395,13 +3395,13 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
-        <v>75.65884162490515</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="37">
@@ -3462,10 +3462,10 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -3502,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>215</v>
+        <v>179.7283339446664</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3553,13 +3553,13 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
     </row>
     <row r="39">
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -3620,22 +3620,22 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>27.00613311885776</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>215</v>
+        <v>51.5721175443767</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
         <v>205.6826957773044</v>
@@ -3705,13 +3705,13 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -3736,19 +3736,19 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>177.9933921796109</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3772,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3787,16 +3787,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="Y41" t="n">
-        <v>187.6104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3809,28 +3809,28 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>50.78666602119189</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>91.28192204366435</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3863,16 +3863,16 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="V42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3942,10 +3942,10 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.08</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="C8" t="n">
-        <v>2.08</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="D8" t="n">
-        <v>2.08</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="E8" t="n">
-        <v>2.08</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>65.87777657221105</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K8" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L8" t="n">
-        <v>52.52000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M8" t="n">
-        <v>78.26000000000001</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N8" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O8" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R8" t="n">
-        <v>67.64575836914665</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S8" t="n">
-        <v>67.64575836914665</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T8" t="n">
-        <v>41.38313210652039</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U8" t="n">
-        <v>41.38313210652039</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V8" t="n">
-        <v>41.38313210652039</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W8" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X8" t="n">
-        <v>15.12050584389412</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.08</v>
+        <v>91.75685858698967</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F9" t="n">
-        <v>81.62201144066449</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G9" t="n">
-        <v>55.35938517803824</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L9" t="n">
-        <v>2.08</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M9" t="n">
-        <v>26.78000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N9" t="n">
-        <v>52.52000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="O9" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="C10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="D10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="E10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="F10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="I10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="J10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N10" t="n">
-        <v>79.3</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P10" t="n">
-        <v>100.8903465994381</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="Q10" t="n">
-        <v>74.62772033681188</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="R10" t="n">
-        <v>48.36509407418561</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="S10" t="n">
-        <v>22.10246781155935</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="U10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="V10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="X10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.08</v>
+        <v>24.54405948333093</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F11" t="n">
-        <v>77.73737373737373</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="G11" t="n">
-        <v>51.47474747474747</v>
+        <v>65.87777657221105</v>
       </c>
       <c r="H11" t="n">
-        <v>25.2121212121212</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L11" t="n">
-        <v>27.82</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M11" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N11" t="n">
-        <v>79.3</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F12" t="n">
-        <v>81.62201144066449</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="G12" t="n">
-        <v>55.35938517803824</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="H12" t="n">
-        <v>29.09675891541198</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L12" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M12" t="n">
-        <v>27.82</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="N12" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y12" t="n">
-        <v>81.62201144066449</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G13" t="n">
-        <v>103.3623149756393</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="H13" t="n">
-        <v>77.09968871301299</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I13" t="n">
-        <v>50.83706245038672</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J13" t="n">
-        <v>24.57443618776046</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.3</v>
+        <v>78.14188814362403</v>
       </c>
       <c r="O13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F14" t="n">
-        <v>92.93786803496215</v>
+        <v>91.75685858698967</v>
       </c>
       <c r="G14" t="n">
-        <v>66.67524177233588</v>
+        <v>65.87777657221105</v>
       </c>
       <c r="H14" t="n">
-        <v>40.41261550970962</v>
+        <v>39.99869455743244</v>
       </c>
       <c r="I14" t="n">
-        <v>14.14998924708335</v>
+        <v>14.11961254265382</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>2.08</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L14" t="n">
-        <v>27.82</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M14" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N14" t="n">
-        <v>79.3</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O14" t="n">
-        <v>79.3</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F15" t="n">
-        <v>80.86787878787879</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G15" t="n">
-        <v>54.60525252525252</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H15" t="n">
-        <v>28.34262626262626</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M15" t="n">
-        <v>27.82</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N15" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G16" t="n">
-        <v>103.72303834074</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="H16" t="n">
-        <v>77.46041207811371</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="F17" t="n">
-        <v>73.62555634894463</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="G17" t="n">
-        <v>70.87564581273992</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="H17" t="n">
-        <v>42.59281752991163</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="I17" t="n">
-        <v>14.30998924708335</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>28.84</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L17" t="n">
-        <v>56.56</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M17" t="n">
-        <v>56.56</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="N17" t="n">
-        <v>56.56</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.9083846317729</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y17" t="n">
-        <v>73.62555634894463</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.43434343434343</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="C18" t="n">
-        <v>27.15151515151514</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="D18" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>28.84</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>28.84</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="M18" t="n">
-        <v>28.84</v>
+        <v>28.41772601812563</v>
       </c>
       <c r="N18" t="n">
-        <v>56.56</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O18" t="n">
-        <v>56.56</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="T18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="U18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="V18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="W18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="X18" t="n">
-        <v>83.71717171717171</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="Y18" t="n">
-        <v>55.43434343434343</v>
+        <v>57.94462678914073</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S19" t="n">
-        <v>87.08848484848485</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="T19" t="n">
-        <v>58.80565656565657</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="U19" t="n">
-        <v>30.52282828282829</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="V19" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W19" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X19" t="n">
-        <v>30.52282828282829</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>251.781970137241</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="C20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T20" t="n">
-        <v>738.6506570059279</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="U20" t="n">
-        <v>495.2163135715845</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="V20" t="n">
-        <v>251.781970137241</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="W20" t="n">
-        <v>251.781970137241</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="X20" t="n">
-        <v>251.781970137241</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="Y20" t="n">
-        <v>251.781970137241</v>
+        <v>601.5428246748836</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.28</v>
+        <v>489.203140025706</v>
       </c>
       <c r="C21" t="n">
-        <v>19.28</v>
+        <v>314.750110744579</v>
       </c>
       <c r="D21" t="n">
-        <v>19.28</v>
+        <v>165.8157010833278</v>
       </c>
       <c r="E21" t="n">
-        <v>19.28</v>
+        <v>165.8157010833278</v>
       </c>
       <c r="F21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M21" t="n">
-        <v>234.7819638733197</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N21" t="n">
-        <v>473.3719638733197</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O21" t="n">
-        <v>711.9619638733197</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>917.7370586902109</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>862.8304705528857</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U21" t="n">
-        <v>634.6068522892747</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V21" t="n">
-        <v>634.6068522892747</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W21" t="n">
-        <v>391.1725088549313</v>
+        <v>518.4217842253022</v>
       </c>
       <c r="X21" t="n">
-        <v>183.3210086493984</v>
+        <v>518.4217842253022</v>
       </c>
       <c r="Y21" t="n">
-        <v>19.28</v>
+        <v>518.4217842253022</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C23" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D23" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E23" t="n">
-        <v>487.3862413384025</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F23" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>243.9518979040591</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>742.8341567219593</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>499.3853800778592</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>255.9366034337592</v>
       </c>
       <c r="W23" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X23" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y23" t="n">
-        <v>720.5656565656566</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>588.3960608094349</v>
+        <v>243.4632136343998</v>
       </c>
       <c r="C24" t="n">
-        <v>588.3960608094349</v>
+        <v>69.01018435327282</v>
       </c>
       <c r="D24" t="n">
-        <v>588.3960608094349</v>
+        <v>69.01018435327282</v>
       </c>
       <c r="E24" t="n">
-        <v>429.1586058039794</v>
+        <v>69.01018435327282</v>
       </c>
       <c r="F24" t="n">
-        <v>282.6240478308644</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G24" t="n">
-        <v>143.8932224134799</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H24" t="n">
-        <v>30.52408682105919</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>19.28</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M24" t="n">
-        <v>257.87</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N24" t="n">
-        <v>496.46</v>
+        <v>726.4525409563269</v>
       </c>
       <c r="O24" t="n">
-        <v>711.9619638733197</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S24" t="n">
-        <v>790.5826554506689</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T24" t="n">
-        <v>588.3960608094349</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="U24" t="n">
-        <v>588.3960608094349</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="V24" t="n">
-        <v>588.3960608094349</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="W24" t="n">
-        <v>588.3960608094349</v>
+        <v>619.4388494194218</v>
       </c>
       <c r="X24" t="n">
-        <v>588.3960608094349</v>
+        <v>619.4388494194218</v>
       </c>
       <c r="Y24" t="n">
-        <v>588.3960608094349</v>
+        <v>411.6785506544679</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="C26" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="D26" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="E26" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
       <c r="F26" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X26" t="n">
-        <v>720.5656565656566</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y26" t="n">
-        <v>506.1486868686869</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M27" t="n">
-        <v>613.1906659261865</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N27" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="O27" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>933.94157013523</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>933.94157013523</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>933.94157013523</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U27" t="n">
-        <v>705.717951871619</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V27" t="n">
-        <v>470.5658436398763</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W27" t="n">
-        <v>227.1315002055328</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X27" t="n">
-        <v>19.28</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y27" t="n">
-        <v>19.28</v>
+        <v>49.38115216564972</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>829.4677095097293</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D29" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V29" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W29" t="n">
-        <v>477.1313131313132</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X29" t="n">
-        <v>233.6969696969697</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y29" t="n">
-        <v>19.28</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>842.6587650651319</v>
+        <v>492.4565854669654</v>
       </c>
       <c r="C30" t="n">
-        <v>668.2057357840049</v>
+        <v>318.0035561858384</v>
       </c>
       <c r="D30" t="n">
-        <v>668.2057357840049</v>
+        <v>318.0035561858384</v>
       </c>
       <c r="E30" t="n">
-        <v>508.9682807785495</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="F30" t="n">
-        <v>362.4337228054344</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G30" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>144.6375600578374</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="M30" t="n">
-        <v>383.2275600578374</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N30" t="n">
-        <v>621.8175600578375</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O30" t="n">
-        <v>860.4075600578375</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="U30" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="V30" t="n">
-        <v>964</v>
+        <v>660.701031422288</v>
       </c>
       <c r="W30" t="n">
-        <v>964</v>
+        <v>660.6719224870335</v>
       </c>
       <c r="X30" t="n">
-        <v>964</v>
+        <v>660.6719224870335</v>
       </c>
       <c r="Y30" t="n">
-        <v>842.6587650651319</v>
+        <v>660.6719224870335</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="C31" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="D31" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="E31" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="F31" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="G31" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="H31" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="I31" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="J31" t="n">
-        <v>19.28</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>849.9083846317729</v>
+        <v>447.4031231009394</v>
       </c>
       <c r="C32" t="n">
-        <v>849.9083846317729</v>
+        <v>447.4031231009394</v>
       </c>
       <c r="D32" t="n">
-        <v>849.9083846317729</v>
+        <v>447.4031231009394</v>
       </c>
       <c r="E32" t="n">
-        <v>632.7366674600557</v>
+        <v>447.4031231009394</v>
       </c>
       <c r="F32" t="n">
-        <v>415.5649502883385</v>
+        <v>447.4031231009394</v>
       </c>
       <c r="G32" t="n">
-        <v>198.3932331166214</v>
+        <v>229.833428471618</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>229.833428471618</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L32" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M32" t="n">
-        <v>513.1408574955809</v>
+        <v>506.5265183822256</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>712.3810405894649</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R32" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S32" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T32" t="n">
-        <v>849.9083846317729</v>
+        <v>664.9728177302609</v>
       </c>
       <c r="U32" t="n">
-        <v>849.9083846317729</v>
+        <v>447.4031231009394</v>
       </c>
       <c r="V32" t="n">
-        <v>849.9083846317729</v>
+        <v>447.4031231009394</v>
       </c>
       <c r="W32" t="n">
-        <v>849.9083846317729</v>
+        <v>447.4031231009394</v>
       </c>
       <c r="X32" t="n">
-        <v>849.9083846317729</v>
+        <v>447.4031231009394</v>
       </c>
       <c r="Y32" t="n">
-        <v>849.9083846317729</v>
+        <v>447.4031231009394</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>232.8813894220949</v>
+        <v>558.2198666437646</v>
       </c>
       <c r="C33" t="n">
-        <v>166.1344096612513</v>
+        <v>558.2198666437646</v>
       </c>
       <c r="D33" t="n">
-        <v>17.2</v>
+        <v>409.2854569825133</v>
       </c>
       <c r="E33" t="n">
-        <v>17.2</v>
+        <v>409.2854569825133</v>
       </c>
       <c r="F33" t="n">
-        <v>17.2</v>
+        <v>262.7508990093983</v>
       </c>
       <c r="G33" t="n">
-        <v>17.2</v>
+        <v>124.0200735920138</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>17.98565246742797</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L33" t="n">
-        <v>355.4075600578374</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M33" t="n">
-        <v>568.2575600578374</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="N33" t="n">
-        <v>781.1075600578374</v>
+        <v>465.6924554125641</v>
       </c>
       <c r="O33" t="n">
-        <v>860</v>
+        <v>678.932513118762</v>
       </c>
       <c r="P33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S33" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="T33" t="n">
-        <v>657.813405358766</v>
+        <v>558.2198666437646</v>
       </c>
       <c r="U33" t="n">
-        <v>657.813405358766</v>
+        <v>558.2198666437646</v>
       </c>
       <c r="V33" t="n">
-        <v>657.813405358766</v>
+        <v>558.2198666437646</v>
       </c>
       <c r="W33" t="n">
-        <v>440.6416881870488</v>
+        <v>558.2198666437646</v>
       </c>
       <c r="X33" t="n">
-        <v>440.6416881870488</v>
+        <v>558.2198666437646</v>
       </c>
       <c r="Y33" t="n">
-        <v>232.8813894220949</v>
+        <v>558.2198666437646</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y34" t="n">
-        <v>39.69443618776046</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>17.2</v>
+        <v>426.43660147347</v>
       </c>
       <c r="C35" t="n">
-        <v>17.2</v>
+        <v>426.43660147347</v>
       </c>
       <c r="D35" t="n">
-        <v>17.2</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="E35" t="n">
-        <v>17.2</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>22.36462077340309</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L35" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R35" t="n">
-        <v>698.5254372164702</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S35" t="n">
-        <v>698.5254372164702</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T35" t="n">
-        <v>698.5254372164702</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U35" t="n">
-        <v>698.5254372164702</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V35" t="n">
-        <v>698.5254372164702</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W35" t="n">
-        <v>668.7151515151515</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X35" t="n">
-        <v>451.5434343434343</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="Y35" t="n">
-        <v>234.3717171717172</v>
+        <v>426.43660147347</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>441.9442460822117</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C36" t="n">
-        <v>267.4912168010848</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D36" t="n">
-        <v>267.4912168010848</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E36" t="n">
-        <v>108.2537617956292</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F36" t="n">
-        <v>108.2537617956292</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G36" t="n">
-        <v>108.2537617956292</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H36" t="n">
-        <v>108.2537617956292</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I36" t="n">
-        <v>17.95413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L36" t="n">
-        <v>17.2</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M36" t="n">
-        <v>230.05</v>
+        <v>396.2978968992348</v>
       </c>
       <c r="N36" t="n">
-        <v>395.1119638733197</v>
+        <v>396.2978968992348</v>
       </c>
       <c r="O36" t="n">
-        <v>607.9619638733197</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P36" t="n">
-        <v>790.6054414866707</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S36" t="n">
-        <v>686.5826554506689</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T36" t="n">
-        <v>686.5826554506689</v>
+        <v>659.389396090879</v>
       </c>
       <c r="U36" t="n">
-        <v>686.5826554506689</v>
+        <v>659.389396090879</v>
       </c>
       <c r="V36" t="n">
-        <v>686.5826554506689</v>
+        <v>659.389396090879</v>
       </c>
       <c r="W36" t="n">
-        <v>686.5826554506689</v>
+        <v>441.8197014615575</v>
       </c>
       <c r="X36" t="n">
-        <v>686.5826554506689</v>
+        <v>233.9682012560247</v>
       </c>
       <c r="Y36" t="n">
-        <v>610.1595831022798</v>
+        <v>26.2079024910708</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="U37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>632.7366674600557</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="C38" t="n">
-        <v>451.5434343434343</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="D38" t="n">
-        <v>451.5434343434343</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="E38" t="n">
-        <v>451.5434343434343</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="F38" t="n">
-        <v>234.3717171717172</v>
+        <v>198.7752914759215</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L38" t="n">
-        <v>300.290857495581</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="R38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="S38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="T38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="U38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="V38" t="n">
-        <v>849.9083846317729</v>
+        <v>851.4843753638859</v>
       </c>
       <c r="W38" t="n">
-        <v>849.9083846317729</v>
+        <v>633.9146807345644</v>
       </c>
       <c r="X38" t="n">
-        <v>849.9083846317729</v>
+        <v>416.3449861052429</v>
       </c>
       <c r="Y38" t="n">
-        <v>849.9083846317729</v>
+        <v>198.7752914759215</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.2</v>
+        <v>191.6845490957693</v>
       </c>
       <c r="C39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L39" t="n">
-        <v>38.80652238664919</v>
+        <v>230.4715775208402</v>
       </c>
       <c r="M39" t="n">
-        <v>251.6565223866492</v>
+        <v>443.7116352270382</v>
       </c>
       <c r="N39" t="n">
-        <v>464.5065223866492</v>
+        <v>648.335933025915</v>
       </c>
       <c r="O39" t="n">
-        <v>677.3565223866492</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S39" t="n">
-        <v>686.5826554506689</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T39" t="n">
-        <v>686.5826554506689</v>
+        <v>659.389396090879</v>
       </c>
       <c r="U39" t="n">
-        <v>659.3037331083883</v>
+        <v>659.389396090879</v>
       </c>
       <c r="V39" t="n">
-        <v>442.1320159366711</v>
+        <v>659.389396090879</v>
       </c>
       <c r="W39" t="n">
-        <v>224.9602987649539</v>
+        <v>607.2963480662561</v>
       </c>
       <c r="X39" t="n">
-        <v>224.9602987649539</v>
+        <v>399.4448478607232</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.2</v>
+        <v>191.6845490957693</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>752.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>791.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>835.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U40" t="n">
-        <v>860</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V40" t="n">
-        <v>860</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17.04</v>
+        <v>628.0253748412023</v>
       </c>
       <c r="C41" t="n">
-        <v>17.04</v>
+        <v>628.0253748412023</v>
       </c>
       <c r="D41" t="n">
-        <v>17.04</v>
+        <v>628.0253748412023</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>412.4453105812599</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>412.4453105812599</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>196.8652463213176</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>196.8652463213176</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>17.04</v>
+        <v>17.62165426160527</v>
       </c>
       <c r="L41" t="n">
-        <v>197.1158515846586</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="R41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="S41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="T41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="U41" t="n">
-        <v>852</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="V41" t="n">
-        <v>636.8484848484849</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="W41" t="n">
-        <v>421.6969696969697</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="X41" t="n">
-        <v>206.5454545454546</v>
+        <v>628.0253748412023</v>
       </c>
       <c r="Y41" t="n">
-        <v>17.04</v>
+        <v>628.0253748412023</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>421.6969696969697</v>
+        <v>430.2654900038965</v>
       </c>
       <c r="C42" t="n">
-        <v>370.3973070493012</v>
+        <v>255.8124607227695</v>
       </c>
       <c r="D42" t="n">
-        <v>221.4628973880499</v>
+        <v>255.8124607227695</v>
       </c>
       <c r="E42" t="n">
-        <v>221.4628973880499</v>
+        <v>163.6084990625025</v>
       </c>
       <c r="F42" t="n">
-        <v>221.4628973880499</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>221.4628973880499</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>108.0937617956292</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.79413265278571</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L42" t="n">
-        <v>227.91</v>
+        <v>219.8269915258632</v>
       </c>
       <c r="M42" t="n">
-        <v>227.91</v>
+        <v>431.1170125070327</v>
       </c>
       <c r="N42" t="n">
-        <v>389.0919638733197</v>
+        <v>642.4070334882022</v>
       </c>
       <c r="O42" t="n">
-        <v>599.9619638733197</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="U42" t="n">
-        <v>852</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="V42" t="n">
-        <v>636.8484848484849</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="W42" t="n">
-        <v>421.6969696969697</v>
+        <v>638.1169902094293</v>
       </c>
       <c r="X42" t="n">
-        <v>421.6969696969697</v>
+        <v>430.2654900038965</v>
       </c>
       <c r="Y42" t="n">
-        <v>421.6969696969697</v>
+        <v>430.2654900038965</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="T43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="U43" t="n">
-        <v>151.5722904902707</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8433,22 +8433,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>245.0393459944755</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L8" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M8" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>229.4130635965909</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O8" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P8" t="n">
-        <v>257.2329957552695</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L9" t="n">
-        <v>138.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M9" t="n">
-        <v>167.0835288715133</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N9" t="n">
-        <v>157.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O9" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,13 +8594,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O10" t="n">
         <v>163.0416663658825</v>
@@ -8670,19 +8670,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L11" t="n">
-        <v>261.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M11" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>255.0333547912217</v>
       </c>
       <c r="O11" t="n">
-        <v>255.0477063711817</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P11" t="n">
         <v>231.2329957552695</v>
@@ -8749,25 +8749,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>163.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L12" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>142.1340339220183</v>
+        <v>166.719161836058</v>
       </c>
       <c r="N12" t="n">
-        <v>156.2912070328283</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O12" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>220.0898510449805</v>
+        <v>244.6749789590202</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>256.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N14" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>230.0982114216867</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P14" t="n">
-        <v>256.1824907047645</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M15" t="n">
-        <v>168.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N15" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>167.5457393939394</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>246.9585379136674</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>255.8883403615408</v>
       </c>
       <c r="O17" t="n">
-        <v>258.0982114216868</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,25 +9223,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>164.7101258430459</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>168.6093106869682</v>
       </c>
       <c r="N18" t="n">
-        <v>159.3417120833333</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>161.5644326746464</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9396,7 +9396,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P20" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q20" t="n">
         <v>212.3149906599047</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>233.1889872709904</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>210.0772877358491</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9700,22 +9700,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>360.2749958316361</v>
+        <v>382.6009056104135</v>
       </c>
       <c r="P24" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9858,7 +9858,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M26" t="n">
         <v>449.5135334928325</v>
@@ -9870,7 +9870,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P26" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q26" t="n">
         <v>212.3149906599047</v>
@@ -9937,13 +9937,13 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L27" t="n">
-        <v>370.8403453034592</v>
+        <v>299.7328472056018</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>301.2062135585481</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
         <v>142.5962444444444</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.1454125711647</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10107,7 +10107,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P29" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10174,19 +10174,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>299.7328472056018</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
-        <v>238.6132356387368</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q30" t="n">
         <v>139.9817740860215</v>
@@ -10335,16 +10335,16 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>438.6332444111135</v>
       </c>
       <c r="N32" t="n">
-        <v>338.5081515458031</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O32" t="n">
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>321.7987081714826</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10411,19 +10411,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L33" t="n">
-        <v>353.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>242.3147604003904</v>
       </c>
       <c r="O33" t="n">
-        <v>222.2855777193561</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P33" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
         <v>139.9817740860215</v>
@@ -10566,13 +10566,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
@@ -10645,19 +10645,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>183.0115685892478</v>
       </c>
       <c r="N36" t="n">
-        <v>298.07096852103</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P36" t="n">
         <v>318.4627686399372</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.1454125711647</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>346.5074603610916</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10885,19 +10885,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
-        <v>160.3791498673986</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>338.0329219811887</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P39" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
         <v>139.9817740860215</v>
@@ -11040,13 +11040,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>220.0898510449805</v>
+        <v>220.6430966734834</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>442.6438299680839</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11122,22 +11122,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>343.3554408268194</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>294.1517766018381</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>356.0205080617874</v>
       </c>
       <c r="P42" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22993,16 +22993,16 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>415.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H8" t="n">
-        <v>339.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,16 +23023,16 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>123.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>197.0958495641314</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
         <v>251.3456529078365</v>
@@ -23041,13 +23041,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>323.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>373.3278378705984</v>
+        <v>375.6208755264353</v>
       </c>
     </row>
     <row r="9">
@@ -23069,16 +23069,16 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F9" t="n">
-        <v>122.9150037196417</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G9" t="n">
-        <v>111.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H9" t="n">
-        <v>86.23544423649646</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -23163,7 +23163,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23178,19 +23178,19 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.424580076758535</v>
       </c>
       <c r="Q10" t="n">
-        <v>60.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R10" t="n">
-        <v>151.2933913771695</v>
+        <v>151.6731001825387</v>
       </c>
       <c r="S10" t="n">
-        <v>198.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T10" t="n">
-        <v>208.1233462948377</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U10" t="n">
         <v>286.3190293564909</v>
@@ -23227,19 +23227,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>380.8760457417114</v>
+        <v>396.2589826120931</v>
       </c>
       <c r="G11" t="n">
-        <v>389.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H11" t="n">
-        <v>313.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I11" t="n">
-        <v>187.5750895704059</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J11" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -23306,19 +23306,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
-        <v>145.0692123933839</v>
+        <v>122.502859909153</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -23342,7 +23342,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>78.00362547890099</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
         <v>171.6831711038378</v>
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.7167873157914</v>
+        <v>167.6941187001108</v>
       </c>
       <c r="H13" t="n">
-        <v>136.2271725074396</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I13" t="n">
-        <v>129.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J13" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23464,16 +23464,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F14" t="n">
-        <v>395.924535096324</v>
+        <v>396.2589826120931</v>
       </c>
       <c r="G14" t="n">
-        <v>389.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H14" t="n">
-        <v>313.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I14" t="n">
-        <v>184.4758895704059</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -23543,19 +23543,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>122.1684123933839</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G15" t="n">
-        <v>111.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I15" t="n">
-        <v>63.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7167873157913</v>
+        <v>167.6941187001108</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23701,16 +23701,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>406.8760457417114</v>
+        <v>379.2860204813953</v>
       </c>
       <c r="G17" t="n">
-        <v>412.5803260842924</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>311.4748021157671</v>
+        <v>327.1227972210932</v>
       </c>
       <c r="I17" t="n">
-        <v>182.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -23734,10 +23734,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
-        <v>121.8691179411497</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S17" t="n">
         <v>209.0200695862453</v>
@@ -23771,10 +23771,10 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C18" t="n">
-        <v>144.7084989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D18" t="n">
-        <v>122.7826655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E18" t="n">
         <v>157.6450804554009</v>
@@ -23786,10 +23786,10 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>84.64541897618032</v>
       </c>
       <c r="I18" t="n">
-        <v>89.39663285141508</v>
+        <v>61.80660759109894</v>
       </c>
       <c r="J18" t="n">
         <v>0.7465913262578567</v>
@@ -23816,7 +23816,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
         <v>171.6831711038378</v>
@@ -23834,10 +23834,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>177.7729852034775</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
-        <v>177.6826957773044</v>
+        <v>181.3814015280179</v>
       </c>
     </row>
     <row r="19">
@@ -23898,16 +23898,16 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>201.9941304107861</v>
+        <v>201.5678386764629</v>
       </c>
       <c r="T19" t="n">
-        <v>199.9455894282815</v>
+        <v>200.3555641679654</v>
       </c>
       <c r="U19" t="n">
-        <v>258.3190293564909</v>
+        <v>258.7290040961748</v>
       </c>
       <c r="V19" t="n">
-        <v>252.137643323828</v>
+        <v>224.5476180635119</v>
       </c>
       <c r="W19" t="n">
         <v>286.522998336591</v>
@@ -23916,7 +23916,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y19" t="n">
-        <v>190.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="20">
@@ -23929,10 +23929,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C20" t="n">
-        <v>135.0959413351389</v>
+        <v>270.8624047773015</v>
       </c>
       <c r="D20" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E20" t="n">
         <v>381.9303700722618</v>
@@ -23944,7 +23944,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I20" t="n">
         <v>210.4758895704059</v>
@@ -23974,19 +23974,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
         <v>349.240968717413</v>
@@ -24005,19 +24005,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>137.6067258922671</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>137.3435171632106</v>
@@ -24053,28 +24053,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>43.2820972143999</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -24129,13 +24129,13 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q22" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>177.2933913771695</v>
+        <v>130.2684670434958</v>
       </c>
       <c r="S22" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
         <v>227.9455894282815</v>
@@ -24172,10 +24172,10 @@
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>151.0827489972802</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
         <v>415.302737515135</v>
@@ -24184,10 +24184,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24208,31 +24208,31 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V23" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W23" t="n">
-        <v>349.240968717413</v>
+        <v>114.952062997102</v>
       </c>
       <c r="X23" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y23" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24242,28 +24242,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>95.83746156275438</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>78.26498689856649</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
         <v>0.7465913262578567</v>
@@ -24290,13 +24290,13 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
@@ -24305,13 +24305,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24381,10 +24381,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
-        <v>118.95067573846</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X25" t="n">
         <v>225.7096553890372</v>
@@ -24412,13 +24412,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F26" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G26" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H26" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I26" t="n">
         <v>210.4758895704059</v>
@@ -24445,7 +24445,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>149.8691179411497</v>
@@ -24454,7 +24454,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>20.80116313523413</v>
       </c>
       <c r="U26" t="n">
         <v>251.3456529078365</v>
@@ -24466,10 +24466,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>173.9651386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24479,7 +24479,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>136.7341746849847</v>
       </c>
       <c r="C27" t="n">
         <v>172.7084989883157</v>
@@ -24527,7 +24527,7 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>70.39998858652083</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
         <v>171.6831711038378</v>
@@ -24542,7 +24542,7 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -24615,10 +24615,10 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U28" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W28" t="n">
         <v>286.522998336591</v>
@@ -24637,16 +24637,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>170.4484560200385</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F29" t="n">
         <v>406.8760457417114</v>
@@ -24697,16 +24697,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y29" t="n">
-        <v>173.9651386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,7 +24716,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -24728,16 +24728,16 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -24764,13 +24764,13 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>225.9413820809748</v>
@@ -24779,13 +24779,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>251.6949831609196</v>
+        <v>251.6661653150177</v>
       </c>
       <c r="X30" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>85.55487319178494</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -24795,7 +24795,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>46.6450125965693</v>
+        <v>68.91450442245211</v>
       </c>
       <c r="C31" t="n">
         <v>167.2468210986278</v>
@@ -24822,7 +24822,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K31" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -24883,19 +24883,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F32" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>200.302737515135</v>
+        <v>199.9087398321068</v>
       </c>
       <c r="H32" t="n">
-        <v>160.093501330312</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I32" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>11.94928935461252</v>
@@ -24928,10 +24928,10 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>38.44940750684262</v>
       </c>
       <c r="U32" t="n">
-        <v>251.3456529078365</v>
+        <v>35.95165522480826</v>
       </c>
       <c r="V32" t="n">
         <v>327.7522584701349</v>
@@ -24956,7 +24956,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>106.6289890250806</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -24965,19 +24965,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>112.2354442364965</v>
+        <v>7.26136732315652</v>
       </c>
       <c r="I33" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25001,7 +25001,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>171.6831711038378</v>
@@ -25016,13 +25016,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="34">
@@ -25059,7 +25059,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -25080,7 +25080,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S34" t="n">
         <v>224.0165980369723</v>
@@ -25092,7 +25092,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V34" t="n">
-        <v>141.2201675643428</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
         <v>286.522998336591</v>
@@ -25111,13 +25111,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
-        <v>354.683041620683</v>
+        <v>139.2890439376547</v>
       </c>
       <c r="E35" t="n">
         <v>381.9303700722618</v>
@@ -25129,7 +25129,7 @@
         <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
-        <v>339.4748021157671</v>
+        <v>149.755768956556</v>
       </c>
       <c r="I35" t="n">
         <v>210.4758895704059</v>
@@ -25156,10 +25156,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
         <v>209.0200695862453</v>
@@ -25174,13 +25174,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>319.7287858731075</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>154.731100678469</v>
+        <v>154.3371029954408</v>
       </c>
       <c r="Y35" t="n">
-        <v>171.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="36">
@@ -25190,16 +25190,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>157.6465648002031</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
         <v>145.0692123933839</v>
@@ -25211,10 +25211,10 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25241,10 +25241,10 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>225.9413820809748</v>
@@ -25253,13 +25253,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>251.6949831609196</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>130.0238541523992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -25320,10 +25320,10 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S37" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T37" t="n">
-        <v>227.9455894282815</v>
+        <v>94.75862184291347</v>
       </c>
       <c r="U37" t="n">
         <v>286.3190293564909</v>
@@ -25348,10 +25348,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>185.8915909855524</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
@@ -25360,10 +25360,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
-        <v>200.302737515135</v>
+        <v>235.5744035704686</v>
       </c>
       <c r="H38" t="n">
         <v>339.4748021157671</v>
@@ -25411,13 +25411,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>349.240968717413</v>
+        <v>133.8469710343848</v>
       </c>
       <c r="X38" t="n">
-        <v>369.731100678469</v>
+        <v>154.3371029954408</v>
       </c>
       <c r="Y38" t="n">
-        <v>386.2379386560536</v>
+        <v>170.8439409730254</v>
       </c>
     </row>
     <row r="39">
@@ -25430,7 +25430,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>147.4450655646388</v>
@@ -25478,22 +25478,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>198.9352489621171</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>36.69498316091961</v>
+        <v>200.1228656165429</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -25563,13 +25563,13 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W40" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X40" t="n">
         <v>225.7096553890372</v>
@@ -25594,19 +25594,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
-        <v>381.9303700722618</v>
+        <v>168.5061064549189</v>
       </c>
       <c r="F41" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
-        <v>415.302737515135</v>
+        <v>201.8784738977921</v>
       </c>
       <c r="H41" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>32.48249739079506</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -25630,7 +25630,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
@@ -25645,16 +25645,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
-        <v>114.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
-        <v>136.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X41" t="n">
-        <v>156.731100678469</v>
+        <v>156.3068370611261</v>
       </c>
       <c r="Y41" t="n">
-        <v>198.6275386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="42">
@@ -25667,28 +25667,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>121.9218329671238</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>66.36315841173659</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -25721,16 +25721,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>12.5171184636319</v>
       </c>
       <c r="V42" t="n">
-        <v>19.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>205.6826957773044</v>
@@ -25800,10 +25800,10 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V43" t="n">
-        <v>118.95067573846</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W43" t="n">
         <v>286.522998336591</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350350.0795405005</v>
+        <v>350035.0587549795</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549795</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549795</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351994.6487060303</v>
+        <v>351669.2246312142</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205642</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506779.7343245362</v>
+        <v>506790.0512205639</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.61581059</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488007.1404845365</v>
+        <v>488291.61581059</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486563.0948045364</v>
+        <v>486869.422826439</v>
       </c>
     </row>
     <row r="16">
@@ -26261,46 +26261,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48378.33248915088</v>
+        <v>48378.33248915087</v>
       </c>
       <c r="C2" t="n">
         <v>48378.33248915087</v>
       </c>
       <c r="D2" t="n">
-        <v>51690.99534204103</v>
+        <v>51644.51686548872</v>
       </c>
       <c r="E2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548873</v>
       </c>
       <c r="F2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548872</v>
       </c>
       <c r="G2" t="n">
-        <v>51933.63669433229</v>
+        <v>51885.62330624471</v>
       </c>
       <c r="H2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="I2" t="n">
-        <v>74770.78047411183</v>
+        <v>74772.30263909959</v>
       </c>
       <c r="J2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="K2" t="n">
-        <v>74770.78047411187</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="L2" t="n">
-        <v>72001.05351411185</v>
+        <v>72043.0252835296</v>
       </c>
       <c r="M2" t="n">
-        <v>72001.05351411187</v>
+        <v>72043.02528352958</v>
       </c>
       <c r="N2" t="n">
-        <v>72001.05351411187</v>
+        <v>72043.0252835296</v>
       </c>
       <c r="O2" t="n">
-        <v>71787.99759411189</v>
+        <v>71833.1935317696</v>
       </c>
       <c r="P2" t="n">
         <v>48378.33248915087</v>
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>7958.431053788175</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26371,40 +26371,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="E4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="F4" t="n">
-        <v>22.532822180663</v>
+        <v>22.21667432804714</v>
       </c>
       <c r="G4" t="n">
-        <v>24.1832752112465</v>
+        <v>23.85668684891895</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="M4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="N4" t="n">
-        <v>160.6823863208583</v>
+        <v>160.9678794298453</v>
       </c>
       <c r="O4" t="n">
-        <v>159.2331741996462</v>
+        <v>159.5405981880675</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26475,40 +26475,40 @@
         <v>14750.73248915088</v>
       </c>
       <c r="D6" t="n">
-        <v>8383.682519860369</v>
+        <v>8478.55543273894</v>
       </c>
       <c r="E6" t="n">
-        <v>50087.66251986039</v>
+        <v>50064.58648652713</v>
       </c>
       <c r="F6" t="n">
-        <v>50087.66251986039</v>
+        <v>50064.58648652711</v>
       </c>
       <c r="G6" t="n">
-        <v>49658.88341912104</v>
+        <v>49644.4185221752</v>
       </c>
       <c r="H6" t="n">
-        <v>2469.141330215243</v>
+        <v>2355.314235302259</v>
       </c>
       <c r="I6" t="n">
-        <v>59938.45833021522</v>
+        <v>59939.10137763395</v>
       </c>
       <c r="J6" t="n">
-        <v>59938.45833021525</v>
+        <v>59939.10137763394</v>
       </c>
       <c r="K6" t="n">
-        <v>59938.45833021526</v>
+        <v>59939.10137763394</v>
       </c>
       <c r="L6" t="n">
-        <v>58768.37112779099</v>
+        <v>58786.10234497163</v>
       </c>
       <c r="M6" t="n">
-        <v>58768.37112779102</v>
+        <v>58786.10234497162</v>
       </c>
       <c r="N6" t="n">
-        <v>58768.37112779102</v>
+        <v>58786.10234497163</v>
       </c>
       <c r="O6" t="n">
-        <v>58678.36441991224</v>
+        <v>58697.4577056471</v>
       </c>
       <c r="P6" t="n">
         <v>48378.33248915087</v>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,43 +26950,43 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,22 +35088,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M9" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,13 +35249,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O10" t="n">
         <v>24.58512791403967</v>
@@ -35325,19 +35325,19 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L11" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O11" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35404,25 +35404,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N12" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,16 +35486,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
-        <v>24.58512791403967</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,25 +35878,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36051,7 +36051,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P20" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>91.05495334897203</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.09551364982758</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36355,22 +36355,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>217.6787513871916</v>
+        <v>240.0046611659691</v>
       </c>
       <c r="P24" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36525,7 +36525,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P26" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36592,13 +36592,13 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L27" t="n">
-        <v>232.285965523585</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -36762,7 +36762,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P29" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36829,19 +36829,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>161.1784674257276</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
-        <v>104.6388282244066</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -36990,16 +36990,16 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>208.2870111838408</v>
       </c>
       <c r="N32" t="n">
-        <v>109.0950879492122</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O32" t="n">
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>90.5657124162131</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37066,19 +37066,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>110.973048317057</v>
       </c>
       <c r="O33" t="n">
-        <v>79.6893332749117</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37221,13 +37221,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37300,19 +37300,19 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>40.87753466722953</v>
       </c>
       <c r="N36" t="n">
-        <v>166.7292564376967</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P36" t="n">
         <v>184.4883612256069</v>
@@ -37458,13 +37458,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>104.0555615261842</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>116.1612271338189</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37540,19 +37540,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>21.82477008752444</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>206.6912098978553</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P39" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37695,13 +37695,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.5532456285028686</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>212.2975967408112</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37777,22 +37777,22 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>204.8010610469452</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>162.8100645185048</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P42" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
